--- a/data/trans_dic/IP1008-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos huesos, articulaciones o musculares</t>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 13,9</t>
+          <t>2,33; 13,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,22</t>
+          <t>1,29; 7,01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -792,49 +793,49 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,43</t>
+          <t>0,92; 7,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,98</t>
+          <t>0,94; 5,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,58; 4,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,32 +1338,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1372,12 +1373,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,65</t>
+          <t>0,41; 3,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,3</t>
+          <t>0,41; 2,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,11</t>
+          <t>0,21; 2,09</t>
         </is>
       </c>
     </row>
@@ -1557,37 +1558,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,14</t>
+          <t>0,17; 1,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,22</t>
+          <t>0,19; 1,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,67</t>
+          <t>0,4; 1,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,23</t>
+          <t>0,28; 1,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,97</t>
+          <t>0,17; 0,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,92</t>
+          <t>0,27; 0,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1597,7 +1598,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,94</t>
+          <t>0,32; 0,96</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4063</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1335; 7748</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3744</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4627</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1566; 8537</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3314</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3123</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3082</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4348</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4559</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>646; 5418</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1298; 7831</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3380</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4270</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4430</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4292</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3528</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2861</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2116</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4928</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3527</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>679; 5752</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3369</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3357</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3923</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4500</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>678; 6110</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4591</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1323; 8035</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>718; 7006</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6235</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1184; 7671</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1355; 7909</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2847; 11565</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2018; 9021</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1281; 7323</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>584; 5077</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3760; 12663</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>3337; 12194</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>4688; 13915</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1008-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Provincia-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,51</t>
+          <t>2,33; 13,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,01</t>
+          <t>1,13; 6,74</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,68</t>
+          <t>0,91; 7,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,64</t>
+          <t>0,95; 5,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 8,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,95</t>
+          <t>0,59; 5,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,72</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,5</t>
+          <t>0,41; 2,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,09</t>
+          <t>0,21; 1,86</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,13</t>
+          <t>0,17; 1,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,12</t>
+          <t>0,19; 1,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,64</t>
+          <t>0,4; 1,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,25</t>
+          <t>0,19; 1,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,98</t>
+          <t>0,17; 0,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,68</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,9</t>
+          <t>0,28; 0,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,84</t>
+          <t>0,23; 0,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,96</t>
+          <t>0,29; 0,95</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4063</t>
+          <t>0; 4200</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1335; 7748</t>
+          <t>1337; 7521</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3744</t>
+          <t>0; 3770</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4627</t>
+          <t>0; 4815</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1566; 8537</t>
+          <t>1381; 8217</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3314</t>
+          <t>0; 3580</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>0; 3155</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3082</t>
+          <t>0; 3528</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3745</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4348</t>
+          <t>0; 4360</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4559</t>
+          <t>0; 4293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>646; 5418</t>
+          <t>642; 5357</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1298; 7831</t>
+          <t>1314; 7612</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3380</t>
+          <t>0; 3532</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4270</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3893</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4430</t>
+          <t>0; 3757</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4292</t>
+          <t>0; 4421</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3528</t>
+          <t>0; 3535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>0; 3125</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4928</t>
+          <t>0; 4772</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3527</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>679; 5752</t>
+          <t>682; 5826</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3369</t>
+          <t>0; 3120</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3357</t>
+          <t>0; 3374</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 4593</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4500</t>
+          <t>0; 4645</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>678; 6110</t>
+          <t>0; 5479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>0; 4031</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1323; 8035</t>
+          <t>1314; 7379</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>718; 7006</t>
+          <t>717; 6239</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1184; 7671</t>
+          <t>1183; 7365</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1355; 7909</t>
+          <t>1358; 8233</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2847; 11565</t>
+          <t>2826; 11751</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2018; 9021</t>
+          <t>1378; 8198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1281; 7323</t>
+          <t>1256; 7159</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>584; 5077</t>
+          <t>587; 5421</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3760; 12663</t>
+          <t>3992; 12893</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3337; 12194</t>
+          <t>3368; 11708</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4688; 13915</t>
+          <t>4209; 13786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1008-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,26%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,11</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>2,32; 13,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,74</t>
+          <t>1,34; 7,22</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,22 +850,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,12%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,92; 8,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,59</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,49</t>
+          <t>0,96; 5,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,01</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,41; 3,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,29</t>
+          <t>0,41; 2,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,86</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,32 +1558,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,08</t>
+          <t>0,19; 1,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,16</t>
+          <t>0,17; 0,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,67</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,13</t>
+          <t>0,17; 1,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,96</t>
+          <t>0,19; 1,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,41; 1,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,8</t>
+          <t>0,23; 0,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,95</t>
+          <t>0,29; 0,94</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3592</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1337; 7521</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3770</t>
+          <t>1329; 7975</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1381; 8217</t>
+          <t>1629; 8800</t>
         </is>
       </c>
     </row>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3580</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3155</t>
+          <t>0; 3096</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3528</t>
+          <t>0; 3136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3745</t>
+          <t>0; 3585</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4360</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2086,22 +2086,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,22 +2139,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1442</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4293</t>
+          <t>647; 5949</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>642; 5357</t>
+          <t>0; 4510</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1314; 7612</t>
+          <t>1334; 8305</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2254,22 +2254,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1234</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3532</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>0; 3198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3829</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3757</t>
+          <t>0; 3847</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>0; 4652</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3535</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2575,22 +2575,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1428</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4772</t>
+          <t>0; 3547</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>0; 4423</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>682; 5826</t>
+          <t>0; 5603</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3966</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3120</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3374</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2896,22 +2896,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1409</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4593</t>
+          <t>677; 5983</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4728</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 5479</t>
+          <t>0; 4026</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4031</t>
+          <t>0; 5003</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1314; 7379</t>
+          <t>1313; 7395</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717; 6239</t>
+          <t>729; 7058</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>6235</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1183; 7365</t>
+          <t>1381; 8886</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1358; 8233</t>
+          <t>1282; 7240</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2826; 11751</t>
+          <t>588; 5708</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1378; 8198</t>
+          <t>1167; 7780</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1256; 7159</t>
+          <t>1360; 8640</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>587; 5421</t>
+          <t>2906; 11767</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3992; 12893</t>
+          <t>3899; 12960</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3368; 11708</t>
+          <t>3401; 12177</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4209; 13786</t>
+          <t>4177; 13601</t>
         </is>
       </c>
     </row>
